--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>61.55876716246186</v>
+        <v>10.00329966390005</v>
       </c>
       <c r="D2" t="n">
-        <v>61.75907331581098</v>
+        <v>10.03584941381929</v>
       </c>
       <c r="E2" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F2" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96208437108598</v>
+        <v>7.468838710301472</v>
       </c>
       <c r="D3" t="n">
-        <v>48.01757876167331</v>
+        <v>7.802856548771913</v>
       </c>
       <c r="E3" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F3" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.47586691914325</v>
+        <v>7.714828374360779</v>
       </c>
       <c r="D4" t="n">
-        <v>46.81718412501001</v>
+        <v>7.607792420314127</v>
       </c>
       <c r="E4" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F4" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.31317135480535</v>
+        <v>7.038390345155869</v>
       </c>
       <c r="D5" t="n">
-        <v>43.509733549865</v>
+        <v>7.070331701853062</v>
       </c>
       <c r="E5" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F5" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.24933843759693</v>
+        <v>7.8405174961095</v>
       </c>
       <c r="D6" t="n">
-        <v>45.62404783860808</v>
+        <v>7.413907773773813</v>
       </c>
       <c r="E6" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F6" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.83360324829323</v>
+        <v>2.897960527847649</v>
       </c>
       <c r="D7" t="n">
-        <v>15.2934698308123</v>
+        <v>2.485188847506998</v>
       </c>
       <c r="E7" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F7" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>62.20559344632176</v>
+        <v>10.10840893502729</v>
       </c>
       <c r="D8" t="n">
-        <v>72.65426573492303</v>
+        <v>11.80631818192499</v>
       </c>
       <c r="E8" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F8" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.43130109464596</v>
+        <v>6.082586427879969</v>
       </c>
       <c r="D9" t="n">
-        <v>37.22894997873136</v>
+        <v>6.049704371543846</v>
       </c>
       <c r="E9" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F9" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.65270248338089</v>
+        <v>2.706064153549395</v>
       </c>
       <c r="D10" t="n">
-        <v>11.90357581832414</v>
+        <v>1.934331070477673</v>
       </c>
       <c r="E10" t="n">
-        <v>15.36173819033523</v>
+        <v>2.496282455929475</v>
       </c>
       <c r="F10" t="n">
-        <v>18.39130993647037</v>
+        <v>2.988587864676435</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
